--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9931,6 +9931,444 @@
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>115062089</v>
+      </c>
+      <c r="B84" t="n">
+        <v>5165</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Nordbäcksbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>572047</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6697703</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>115061656</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79433</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>571799</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6697649</v>
+      </c>
+      <c r="S85" t="n">
+        <v>15</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>115061662</v>
+      </c>
+      <c r="B86" t="n">
+        <v>5165</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>571833</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6697659</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>115061660</v>
+      </c>
+      <c r="B87" t="n">
+        <v>5165</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>571846</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6697583</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -10797,10 +10797,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117916886</v>
+        <v>117916895</v>
       </c>
       <c r="B92" t="n">
-        <v>90499</v>
+        <v>79465</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10809,25 +10809,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10837,10 +10837,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>571799</v>
+        <v>572269</v>
       </c>
       <c r="R92" t="n">
-        <v>6697627</v>
+        <v>6697673</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10899,10 +10899,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117916887</v>
+        <v>117916882</v>
       </c>
       <c r="B93" t="n">
-        <v>90499</v>
+        <v>97753</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10911,25 +10911,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10939,10 +10939,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>571801</v>
+        <v>572228</v>
       </c>
       <c r="R93" t="n">
-        <v>6697621</v>
+        <v>6697750</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10983,6 +10983,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11001,10 +11002,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117916912</v>
+        <v>117916897</v>
       </c>
       <c r="B94" t="n">
-        <v>5166</v>
+        <v>96785</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11017,43 +11018,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100526</v>
+        <v>221944</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>571802</v>
+        <v>571755</v>
       </c>
       <c r="R94" t="n">
-        <v>6697623</v>
+        <v>6697748</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11113,10 +11101,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117916885</v>
+        <v>117916883</v>
       </c>
       <c r="B95" t="n">
-        <v>90499</v>
+        <v>5186</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11125,38 +11113,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>572150</v>
+        <v>572265</v>
       </c>
       <c r="R95" t="n">
-        <v>6697737</v>
+        <v>6697717</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11197,6 +11194,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11215,10 +11213,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117916895</v>
+        <v>117916887</v>
       </c>
       <c r="B96" t="n">
-        <v>79465</v>
+        <v>90499</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11227,25 +11225,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11255,10 +11253,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>572269</v>
+        <v>571801</v>
       </c>
       <c r="R96" t="n">
-        <v>6697673</v>
+        <v>6697621</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11317,10 +11315,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117916883</v>
+        <v>117916885</v>
       </c>
       <c r="B97" t="n">
-        <v>5186</v>
+        <v>90499</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11329,47 +11327,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>572265</v>
+        <v>572150</v>
       </c>
       <c r="R97" t="n">
-        <v>6697717</v>
+        <v>6697737</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11410,7 +11399,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11429,10 +11417,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117916894</v>
+        <v>117916912</v>
       </c>
       <c r="B98" t="n">
-        <v>79465</v>
+        <v>5166</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11445,34 +11433,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>572259</v>
+        <v>571802</v>
       </c>
       <c r="R98" t="n">
-        <v>6697676</v>
+        <v>6697623</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11513,6 +11510,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11531,10 +11529,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117916882</v>
+        <v>117916889</v>
       </c>
       <c r="B99" t="n">
-        <v>97753</v>
+        <v>57303</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11543,38 +11541,46 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>572228</v>
+        <v>572182</v>
       </c>
       <c r="R99" t="n">
-        <v>6697750</v>
+        <v>6697565</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11615,7 +11621,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11634,10 +11639,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117916889</v>
+        <v>117916886</v>
       </c>
       <c r="B100" t="n">
-        <v>57303</v>
+        <v>90499</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11650,42 +11655,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>572182</v>
+        <v>571799</v>
       </c>
       <c r="R100" t="n">
-        <v>6697565</v>
+        <v>6697627</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11744,10 +11741,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117916897</v>
+        <v>117916894</v>
       </c>
       <c r="B101" t="n">
-        <v>96785</v>
+        <v>79465</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11760,19 +11757,23 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221944</v>
+        <v>6456</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11780,10 +11781,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>571755</v>
+        <v>572259</v>
       </c>
       <c r="R101" t="n">
-        <v>6697748</v>
+        <v>6697676</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11824,7 +11825,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -10797,10 +10797,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117916895</v>
+        <v>117916897</v>
       </c>
       <c r="B92" t="n">
-        <v>79465</v>
+        <v>96787</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10813,23 +10813,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6456</v>
+        <v>221944</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10837,10 +10833,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>572269</v>
+        <v>571755</v>
       </c>
       <c r="R92" t="n">
-        <v>6697673</v>
+        <v>6697748</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10881,6 +10877,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10899,10 +10896,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117916882</v>
+        <v>117916887</v>
       </c>
       <c r="B93" t="n">
-        <v>97753</v>
+        <v>90501</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10911,25 +10908,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10939,10 +10936,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>572228</v>
+        <v>571801</v>
       </c>
       <c r="R93" t="n">
-        <v>6697750</v>
+        <v>6697621</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10983,7 +10980,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11002,10 +10998,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117916897</v>
+        <v>117916885</v>
       </c>
       <c r="B94" t="n">
-        <v>96785</v>
+        <v>90501</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11014,23 +11010,27 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221944</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11038,10 +11038,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>571755</v>
+        <v>572150</v>
       </c>
       <c r="R94" t="n">
-        <v>6697748</v>
+        <v>6697737</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11082,7 +11082,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11101,10 +11100,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117916883</v>
+        <v>117916895</v>
       </c>
       <c r="B95" t="n">
-        <v>5186</v>
+        <v>79467</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11117,43 +11116,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>105930</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>572265</v>
+        <v>572269</v>
       </c>
       <c r="R95" t="n">
-        <v>6697717</v>
+        <v>6697673</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11194,7 +11184,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11213,10 +11202,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117916887</v>
+        <v>117916886</v>
       </c>
       <c r="B96" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11253,10 +11242,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>571801</v>
+        <v>571799</v>
       </c>
       <c r="R96" t="n">
-        <v>6697621</v>
+        <v>6697627</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11315,10 +11304,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117916885</v>
+        <v>117916912</v>
       </c>
       <c r="B97" t="n">
-        <v>90499</v>
+        <v>5166</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11327,38 +11316,47 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>572150</v>
+        <v>571802</v>
       </c>
       <c r="R97" t="n">
-        <v>6697737</v>
+        <v>6697623</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11399,6 +11397,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11417,10 +11416,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117916912</v>
+        <v>117916882</v>
       </c>
       <c r="B98" t="n">
-        <v>5166</v>
+        <v>97755</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11433,43 +11432,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100526</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>571802</v>
+        <v>572228</v>
       </c>
       <c r="R98" t="n">
-        <v>6697623</v>
+        <v>6697750</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11532,7 +11522,7 @@
         <v>117916889</v>
       </c>
       <c r="B99" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11639,10 +11629,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117916886</v>
+        <v>117916883</v>
       </c>
       <c r="B100" t="n">
-        <v>90499</v>
+        <v>5186</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11651,38 +11641,47 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>571799</v>
+        <v>572265</v>
       </c>
       <c r="R100" t="n">
-        <v>6697627</v>
+        <v>6697717</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11723,6 +11722,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11744,7 +11744,7 @@
         <v>117916894</v>
       </c>
       <c r="B101" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -6019,11 +6019,11 @@
         <v>108892213</v>
       </c>
       <c r="B48" t="n">
-        <v>89832</v>
+        <v>91168</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572147.3954979242</v>
+        <v>572147</v>
       </c>
       <c r="R48" t="n">
-        <v>6697732.178219927</v>
+        <v>6697732</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -6019,7 +6019,7 @@
         <v>108892213</v>
       </c>
       <c r="B48" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6019,7 +6019,7 @@
         <v>108892213</v>
       </c>
       <c r="B48" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -11001,10 +11001,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117916897</v>
+        <v>117916882</v>
       </c>
       <c r="B94" t="n">
-        <v>96789</v>
+        <v>97757</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11017,19 +11017,23 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221944</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11037,10 +11041,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>571755</v>
+        <v>572228</v>
       </c>
       <c r="R94" t="n">
-        <v>6697748</v>
+        <v>6697750</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11100,10 +11104,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117916882</v>
+        <v>117916912</v>
       </c>
       <c r="B95" t="n">
-        <v>97757</v>
+        <v>5166</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11116,34 +11120,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>572228</v>
+        <v>571802</v>
       </c>
       <c r="R95" t="n">
-        <v>6697750</v>
+        <v>6697623</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11203,10 +11216,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117916912</v>
+        <v>117916889</v>
       </c>
       <c r="B96" t="n">
-        <v>5166</v>
+        <v>57306</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11215,34 +11228,33 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -11252,10 +11264,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>571802</v>
+        <v>572182</v>
       </c>
       <c r="R96" t="n">
-        <v>6697623</v>
+        <v>6697565</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11296,7 +11308,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11315,10 +11326,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117916889</v>
+        <v>117916886</v>
       </c>
       <c r="B97" t="n">
-        <v>57306</v>
+        <v>90503</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11331,42 +11342,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>572182</v>
+        <v>571799</v>
       </c>
       <c r="R97" t="n">
-        <v>6697565</v>
+        <v>6697627</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11425,10 +11428,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117916886</v>
+        <v>117916894</v>
       </c>
       <c r="B98" t="n">
-        <v>90503</v>
+        <v>79469</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11437,25 +11440,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11465,10 +11468,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>571799</v>
+        <v>572259</v>
       </c>
       <c r="R98" t="n">
-        <v>6697627</v>
+        <v>6697676</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11527,10 +11530,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117916894</v>
+        <v>117916885</v>
       </c>
       <c r="B99" t="n">
-        <v>79469</v>
+        <v>90503</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11539,25 +11542,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11567,10 +11570,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>572259</v>
+        <v>572150</v>
       </c>
       <c r="R99" t="n">
-        <v>6697676</v>
+        <v>6697737</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11629,10 +11632,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117916885</v>
+        <v>117916883</v>
       </c>
       <c r="B100" t="n">
-        <v>90503</v>
+        <v>5186</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11641,38 +11644,47 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Nordbäcksbo, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>572150</v>
+        <v>572265</v>
       </c>
       <c r="R100" t="n">
-        <v>6697737</v>
+        <v>6697717</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11713,6 +11725,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11728,118 +11741,6 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>117916883</v>
-      </c>
-      <c r="B101" t="n">
-        <v>5186</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Nordbäcksbo, Dlr</t>
-        </is>
-      </c>
-      <c r="Q101" t="n">
-        <v>572265</v>
-      </c>
-      <c r="R101" t="n">
-        <v>6697717</v>
-      </c>
-      <c r="S101" t="n">
-        <v>10</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Hedemora</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Husby</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF101" t="inlineStr"/>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT101" t="inlineStr"/>
-      <c r="AW101" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -6019,7 +6019,7 @@
         <v>108892213</v>
       </c>
       <c r="B48" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -6019,7 +6019,7 @@
         <v>108892213</v>
       </c>
       <c r="B48" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -7632,7 +7632,7 @@
         <v>113630178</v>
       </c>
       <c r="B63" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>113630170</v>
       </c>
       <c r="B64" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>113630169</v>
       </c>
       <c r="B65" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>113630173</v>
       </c>
       <c r="B68" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>113630181</v>
       </c>
       <c r="B71" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>113630168</v>
       </c>
       <c r="B72" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>113630174</v>
       </c>
       <c r="B73" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>113630175</v>
       </c>
       <c r="B74" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>113630186</v>
       </c>
       <c r="B77" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>113630176</v>
       </c>
       <c r="B79" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>113630177</v>
       </c>
       <c r="B80" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>113630180</v>
       </c>
       <c r="B81" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113630179</v>
       </c>
       <c r="B82" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>

--- a/artfynd/A 9053-2020 artfynd.xlsx
+++ b/artfynd/A 9053-2020 artfynd.xlsx
@@ -7632,7 +7632,7 @@
         <v>113630178</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>113630170</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>113630169</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>113630173</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>113630181</v>
       </c>
       <c r="B71" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>113630168</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>113630174</v>
       </c>
       <c r="B73" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>113630175</v>
       </c>
       <c r="B74" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>113630186</v>
       </c>
       <c r="B77" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>113630176</v>
       </c>
       <c r="B79" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>113630177</v>
       </c>
       <c r="B80" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>113630180</v>
       </c>
       <c r="B81" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113630179</v>
       </c>
       <c r="B82" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
